--- a/plantillas/eleccion/Resultado_Computo_Total_UT.xlsx
+++ b/plantillas/eleccion/Resultado_Computo_Total_UT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\eleccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95CF6909-534C-4B46-A659-367965DE656C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F571F2-8F0E-43C2-A2E8-0F8B4E8ED9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A4A74427-8CFC-472D-9C29-4E23C2DF1387}"/>
   </bookViews>
@@ -193,7 +193,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -549,7 +549,7 @@
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
     </row>
@@ -562,13 +562,16 @@
       <c r="B6" s="3"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
       <c r="B8" s="6"/>
-      <c r="K8" s="1" t="s">
+      <c r="K8" s="1"/>
+      <c r="L8" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K9" s="1" t="s">
+      <c r="K9" s="1"/>
+      <c r="L9" s="1" t="s">
         <v>12</v>
       </c>
     </row>
